--- a/backtest_runs/20260410_193731/by_symbol/TSML/TSML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TSML/TSML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-304.9199999999978</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>99695.08</v>
@@ -725,7 +725,7 @@
         <v>-3833.279999999994</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>114103.76</v>
@@ -771,7 +771,7 @@
         <v>-8586.160000000003</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>105517.6</v>
@@ -955,7 +955,7 @@
         <v>-7671.399999999997</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>107022.84</v>
@@ -1001,7 +1001,7 @@
         <v>-4143.040000000001</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>102879.8</v>
@@ -1323,7 +1323,7 @@
         <v>-4409.239999999993</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>114645.84</v>
@@ -1599,7 +1599,7 @@
         <v>-4656.080000000002</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>143380.92</v>
